--- a/survey_templates/039_veterinary_cybersecurity_readiness_survey--survey_templates.xlsx
+++ b/survey_templates/039_veterinary_cybersecurity_readiness_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -719,8 +719,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -748,12 +748,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'location_a'}</t>
+          <t>location_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Location A'}</t>
+          <t>Location A</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'location_b'}</t>
+          <t>location_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Location B'}</t>
+          <t>Location B</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'location_c'}</t>
+          <t>location_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Location C'}</t>
+          <t>Location C</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'location_d'}</t>
+          <t>location_d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Location D'}</t>
+          <t>Location D</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'compliance'}</t>
+          <t>compliance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Compliance'}</t>
+          <t>Compliance</t>
         </is>
       </c>
     </row>
@@ -833,12 +833,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'data_breach'}</t>
+          <t>data_breach</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Data Breach'}</t>
+          <t>Data Breach</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'cyber_insurance'}</t>
+          <t>cyber_insurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Cyber Insurance'}</t>
+          <t>Cyber Insurance</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'it/is_security'}</t>
+          <t>it/is_security</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'IT/IS Security'}</t>
+          <t>IT/IS Security</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'regulatory_compliance'}</t>
+          <t>regulatory_compliance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Regulatory Compliance'}</t>
+          <t>Regulatory Compliance</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'confidential'}</t>
+          <t>confidential</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Confidential'}</t>
+          <t>Confidential</t>
         </is>
       </c>
     </row>
